--- a/docs/DOSSIER_ARCHITECTURE.xlsx
+++ b/docs/DOSSIER_ARCHITECTURE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0236FA5C-24B0-45E4-8C67-02F771F4B31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBABC88B-DC8D-4C1B-B92D-DA2F618C7FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{A43743E9-A460-4B54-BF95-6131C83D39E7}"/>
+    <workbookView xWindow="5604" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{5936F78C-3E19-44A9-8640-2B75517FF165}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>Moteur d'orchestration</t>
   </si>
   <si>
-    <t>jobs_table.csv (136 jobs), IN_COND/OUT_COND, MAX_PARALLEL_JOBS=6 (vagues paralleles)</t>
+    <t>jobs_table.csv (150 jobs), IN_COND/OUT_COND, MAX_PARALLEL_JOBS=6 (vagues paralleles)</t>
   </si>
   <si>
     <t>orchestrator.sh, jobs_table.csv</t>
@@ -337,7 +337,7 @@
         <xdr:cNvPr id="3" name="Image 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A99422A7-025A-45A3-87D4-E125192D0C11}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74FA4209-C5B9-49F7-A5CC-7B0657A72C9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -668,7 +668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6927ADB3-9CEF-4DBD-893C-965C4210017C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB49209-4202-45F4-88DB-99345875F2E6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1083,7 +1083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C352EF01-464B-4C22-9E45-2CD68E90C78A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4225ACE0-BB95-40F1-8A1A-43B08778DA5D}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/docs/DOSSIER_ARCHITECTURE.xlsx
+++ b/docs/DOSSIER_ARCHITECTURE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBABC88B-DC8D-4C1B-B92D-DA2F618C7FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18F3702A-2397-4685-B1E2-4A029FBC085E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5604" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{5936F78C-3E19-44A9-8640-2B75517FF165}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{B8EB5145-5750-43C0-8BCD-2A2342E6B911}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -330,14 +330,14 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>403860</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74FA4209-C5B9-49F7-A5CC-7B0657A72C9B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A19B3A02-41F5-43A0-8165-0F4769768D66}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -360,7 +360,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="381000" y="1143000"/>
-          <a:ext cx="5334000" cy="4267200"/>
+          <a:ext cx="5334000" cy="4182110"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -668,7 +668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB49209-4202-45F4-88DB-99345875F2E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A7778C4-2FFD-4EF5-96BA-98C115E8438F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1083,7 +1083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4225ACE0-BB95-40F1-8A1A-43B08778DA5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBACD3A-A149-45EB-B611-8EFCD19E7D1B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
